--- a/Sponsors_tracker.xlsx
+++ b/Sponsors_tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxime\Desktop\Projet Perso\C3I\Github\Fork\documents_sponsors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90ac2b07ca2a4b78/Documents/GitHub/documents_sponsors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59369859-E3A4-44C0-848D-6D27FAA85ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{59369859-E3A4-44C0-848D-6D27FAA85ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{034FF5DE-74EC-4E4F-AA60-F4513C7A0B63}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
   <si>
     <t>Nom de la compagnie:</t>
   </si>
@@ -360,6 +360,15 @@
   </si>
   <si>
     <t>Maxime Leblanc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.electronicsassemblers.com/</t>
+  </si>
+  <si>
+    <t>Charles-Ariel Dion</t>
+  </si>
+  <si>
+    <t>PCBONLINE</t>
   </si>
 </sst>
 </file>
@@ -424,13 +433,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -792,22 +800,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.28515625" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.7265625" customWidth="1"/>
+    <col min="2" max="2" width="42.36328125" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.453125" customWidth="1"/>
+    <col min="5" max="5" width="25.54296875" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" customWidth="1"/>
+    <col min="8" max="8" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.26953125" customWidth="1"/>
+    <col min="10" max="10" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -842,7 +850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -865,7 +873,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -891,7 +899,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -917,7 +925,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -934,7 +942,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -960,7 +968,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -977,7 +985,7 @@
         <v>45720</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -994,11 +1002,11 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1011,7 +1019,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1028,7 +1036,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1045,7 +1053,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1062,7 +1070,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -1076,7 +1084,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1093,7 +1101,7 @@
         <v>45932</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1110,7 +1118,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -1127,7 +1135,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -1144,7 +1152,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -1161,7 +1169,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1184,7 +1192,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -1198,7 +1206,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -1215,7 +1223,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -1232,7 +1240,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -1249,7 +1257,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>97</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1274,7 +1282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -1291,7 +1299,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1308,11 +1316,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E28" t="s">
@@ -1325,8 +1333,8 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1337,6 +1345,20 @@
       </c>
       <c r="G29" s="4">
         <v>46031</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46066</v>
       </c>
     </row>
   </sheetData>
@@ -1391,26 +1413,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="05dc0aba-4466-4464-ae54-e30ec1d1960e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ab60a15-fb7d-489d-9e0d-4f2626c05be0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100873BCB8DB02F314E9B33D47D2328BEE3" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e554ae5040b51359eb2ce52773233a0a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ab60a15-fb7d-489d-9e0d-4f2626c05be0" xmlns:ns3="05dc0aba-4466-4464-ae54-e30ec1d1960e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="19c39bb3469a366f9905408a925319f0" ns2:_="" ns3:_="">
     <xsd:import namespace="3ab60a15-fb7d-489d-9e0d-4f2626c05be0"/>
@@ -1605,26 +1607,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A185DED4-5536-4DE8-9ED1-973A2272A88F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05dc0aba-4466-4464-ae54-e30ec1d1960e"/>
-    <ds:schemaRef ds:uri="3ab60a15-fb7d-489d-9e0d-4f2626c05be0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E9BF95E-040F-4DB3-8CBA-B5E6AB45C8E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="05dc0aba-4466-4464-ae54-e30ec1d1960e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ab60a15-fb7d-489d-9e0d-4f2626c05be0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9257EC00-C374-4722-9DA7-ED3C4D9C653E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1641,4 +1644,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E9BF95E-040F-4DB3-8CBA-B5E6AB45C8E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A185DED4-5536-4DE8-9ED1-973A2272A88F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05dc0aba-4466-4464-ae54-e30ec1d1960e"/>
+    <ds:schemaRef ds:uri="3ab60a15-fb7d-489d-9e0d-4f2626c05be0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>